--- a/5. Other/Đề xuất mua hàng/Năm 2025/Đề Xuất Mua Linh Kiện Sửa Chữa VNSH02(C43)_101125.xlsx
+++ b/5. Other/Đề xuất mua hàng/Năm 2025/Đề Xuất Mua Linh Kiện Sửa Chữa VNSH02(C43)_101125.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\Đề xuất mua hàng\Năm 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527E65DA-1F3D-4754-9C4D-FA28C32A2205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDD3175-DF18-42A1-9593-D26D04D6E074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>STT</t>
   </si>
@@ -137,13 +137,28 @@
   </si>
   <si>
     <t>MODULE GPS GNSS SKG12BL MT3337</t>
+  </si>
+  <si>
+    <t>SOT23-6/MP62551DJ</t>
+  </si>
+  <si>
+    <t>IC quản lý nguồn</t>
+  </si>
+  <si>
+    <t>Module SIM A7682S</t>
+  </si>
+  <si>
+    <t>Module GPS SIM65M-C</t>
+  </si>
+  <si>
+    <t>Thay thế linh kiện TG102LE-4G (0056)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +208,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,7 +223,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -217,19 +238,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -359,7 +367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,28 +381,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -434,70 +439,106 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,14 +664,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>314739</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>41412</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>24848</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>66260</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>33130</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -653,7 +694,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7984435" y="5425108"/>
+          <a:off x="7984435" y="5607326"/>
           <a:ext cx="5201478" cy="2898913"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -929,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
@@ -941,8 +982,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="7"/>
       <c r="C1" s="32" t="s">
         <v>7</v>
       </c>
@@ -951,16 +992,16 @@
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
       <c r="C2" s="35"/>
       <c r="D2" s="36"/>
       <c r="E2" s="36"/>
       <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="11"/>
       <c r="C3" s="38" t="s">
         <v>14</v>
       </c>
@@ -969,8 +1010,8 @@
       <c r="F3" s="40"/>
     </row>
     <row r="4" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="11"/>
       <c r="C4" s="41" t="s">
         <v>15</v>
       </c>
@@ -979,8 +1020,8 @@
       <c r="F4" s="43"/>
     </row>
     <row r="5" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="44" t="s">
         <v>16</v>
       </c>
@@ -989,42 +1030,42 @@
       <c r="F5" s="46"/>
     </row>
     <row r="6" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
     </row>
     <row r="7" spans="1:15" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
@@ -1039,7 +1080,7 @@
       <c r="D8" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="52" t="s">
         <v>24</v>
       </c>
       <c r="F8" s="47" t="s">
@@ -1051,259 +1092,318 @@
       <c r="B9" s="47"/>
       <c r="C9" s="47"/>
       <c r="D9" s="47"/>
-      <c r="E9" s="49"/>
+      <c r="E9" s="53"/>
       <c r="F9" s="47"/>
     </row>
-    <row r="10" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>1</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="49" t="s">
         <v>5</v>
       </c>
       <c r="E10" s="4">
         <v>50</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="28" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="6" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" s="5" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>2</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="50"/>
       <c r="E11" s="4">
         <v>50</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="29" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="50"/>
       <c r="E12" s="4">
         <v>40</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>4</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="50"/>
       <c r="E13" s="4">
         <v>20</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>5</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="50"/>
       <c r="E14" s="4">
         <v>20</v>
       </c>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="28"/>
+    </row>
+    <row r="15" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="4">
         <v>20</v>
       </c>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="29"/>
+    </row>
+    <row r="16" spans="1:15" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>7</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="50"/>
       <c r="E16" s="4">
         <v>30</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="6" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" s="5" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>8</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="4">
         <v>10</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" s="6" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="28"/>
+    </row>
+    <row r="18" spans="1:6" s="5" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>9</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="4">
         <v>50</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>10</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="27">
+        <v>50</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>11</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="E20" s="27">
+        <v>20</v>
+      </c>
+      <c r="F20" s="30"/>
+    </row>
     <row r="21" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="3"/>
+      <c r="B21" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="60"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="27">
+        <v>20</v>
+      </c>
+      <c r="F21" s="30"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="55"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="55"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="58"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="16" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="16" t="s">
+      <c r="E24" s="19"/>
+      <c r="F24" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+    <row r="25" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="18" t="s">
+      <c r="B25" s="26"/>
+      <c r="C25" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D25" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="18" t="s">
+      <c r="E25" s="20"/>
+      <c r="F25" s="17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="17"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="17"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="17"/>
-    </row>
     <row r="26" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="16"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="16"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="15"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="16" t="s">
+      <c r="B30" s="24"/>
+      <c r="C30" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="16" t="s">
+      <c r="E30" s="19"/>
+      <c r="F30" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D10:D21"/>
+    <mergeCell ref="C10:C19"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="C10:C18"/>
-    <mergeCell ref="D10:D18"/>
     <mergeCell ref="C1:F2"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
